--- a/juros.xlsx
+++ b/juros.xlsx
@@ -497,7 +497,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">B3 * 1</f>
+        <f aca="false">B3 * A6</f>
         <v>30</v>
       </c>
       <c r="D6" s="9" t="n">
@@ -518,7 +518,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="11" t="n">
-        <f aca="false"> B3* 2</f>
+        <f aca="false"> B3 * A7</f>
         <v>60</v>
       </c>
       <c r="D7" s="11" t="n">
@@ -539,7 +539,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false"> B3 *3</f>
+        <f aca="false"> B3 * A8</f>
         <v>90</v>
       </c>
       <c r="D8" s="9" t="n">
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="11" t="n">
-        <f aca="false"> B3 * 4</f>
+        <f aca="false"> B3 * A9</f>
         <v>120</v>
       </c>
       <c r="D9" s="11" t="n">
@@ -581,7 +581,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false"> B3 *5</f>
+        <f aca="false"> B3 * A10</f>
         <v>150</v>
       </c>
       <c r="D10" s="9" t="n">
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="11" t="n">
-        <f aca="false"> B3 * 6</f>
+        <f aca="false"> B3 * A11</f>
         <v>180</v>
       </c>
       <c r="D11" s="11" t="n">
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false"> B3 * 7</f>
+        <f aca="false"> B3 * A12</f>
         <v>210</v>
       </c>
       <c r="D12" s="9" t="n">
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="11" t="n">
-        <f aca="false"> B3 * 8</f>
+        <f aca="false"> B3 * A13</f>
         <v>240</v>
       </c>
       <c r="D13" s="11" t="n">
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false"> B3 * 9</f>
+        <f aca="false"> B3 * A14</f>
         <v>270</v>
       </c>
       <c r="D14" s="9" t="n">
@@ -686,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="11" t="n">
-        <f aca="false"> B3 * 10</f>
+        <f aca="false"> B3 * A15</f>
         <v>300</v>
       </c>
       <c r="D15" s="11" t="n">
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false"> B3 *11</f>
+        <f aca="false"> B3 * A16</f>
         <v>330</v>
       </c>
       <c r="D16" s="9" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="11" t="n">
-        <f aca="false"> B3 * 12</f>
+        <f aca="false"> B3 * A17</f>
         <v>360</v>
       </c>
       <c r="D17" s="11" t="n">

--- a/juros.xlsx
+++ b/juros.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="n">
-        <v>0.03</v>
+        <v>0.0492122564005581</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -501,12 +501,12 @@
         <v>30</v>
       </c>
       <c r="D6" s="9" t="n">
-        <f aca="false"> B6 / (1 + D3  * C6 / B3)</f>
-        <v>0.970873786407767</v>
+        <f aca="false"> B6 / (1 + D3 * C6 / B3)</f>
+        <v>0.953095995495338</v>
       </c>
       <c r="E6" s="9" t="n">
-        <f aca="false"> B6 / (1 + D3 ) ^ (C6 / B3)</f>
-        <v>0.970873786407767</v>
+        <f aca="false"> B6 / (1 + D3) ^ (C6 / B3)</f>
+        <v>0.953095995495338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -522,12 +522,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="11" t="n">
-        <f aca="false"> B7 / (1 + D3  * C7 / B3)</f>
-        <v>0.943396226415094</v>
+        <f aca="false"> B7 / (1 + D3 * C7 / B3)</f>
+        <v>0.910394832185489</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false"> B7 / (1 + D3 ) ^ (C7 / B3)</f>
-        <v>0.942595909133754</v>
+        <f aca="false"> B7 / (1 + D3) ^ (C7 / B3)</f>
+        <v>0.90839197662925</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -543,12 +543,12 @@
         <v>90</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false"> B8 / (1 + D3  * C8 / B3)</f>
-        <v>0.91743119266055</v>
+        <f aca="false"> B8 / (1 + D3 * C8 / B3)</f>
+        <v>0.871355839091515</v>
       </c>
       <c r="E8" s="9" t="n">
-        <f aca="false"> B8 / (1 + D3 ) ^ (C8 / B3)</f>
-        <v>0.91514165935316</v>
+        <f aca="false"> B8 / (1 + D3) ^ (C8 / B3)</f>
+        <v>0.865784755265433</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,11 +564,11 @@
         <v>120</v>
       </c>
       <c r="D9" s="11" t="n">
-        <f aca="false"> B9 / (1 + D3  * C9 / B3)</f>
+        <f aca="false"> B9 / (1 + D3 * C9 / B3)</f>
         <v>0</v>
       </c>
       <c r="E9" s="11" t="n">
-        <f aca="false"> B9 / (1 + D3 ) ^ (C9 / B3)</f>
+        <f aca="false"> B9 / (1 + D3) ^ (C9 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -585,11 +585,11 @@
         <v>150</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false"> B10 / (1 + D3  * C10 / B3)</f>
+        <f aca="false"> B10 / (1 + D3 * C10 / B3)</f>
         <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false"> B10 / (1 + D3 ) ^ (C10 / B3)</f>
+        <f aca="false"> B10 / (1 + D3) ^ (C10 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -606,11 +606,11 @@
         <v>180</v>
       </c>
       <c r="D11" s="11" t="n">
-        <f aca="false"> B11 / (1 + D3  * C11 / B3)</f>
+        <f aca="false"> B11 / (1 + D3 * C11 / B3)</f>
         <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
-        <f aca="false"> B11 / (1 + D3 ) ^ (C11 / B3)</f>
+        <f aca="false"> B11 / (1 + D3) ^ (C11 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -627,11 +627,11 @@
         <v>210</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false"> B12 / (1 + D3  * C12 / B3)</f>
+        <f aca="false"> B12 / (1 + D3 * C12 / B3)</f>
         <v>0</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false"> B12 / (1 + D3 ) ^ (C12 / B3)</f>
+        <f aca="false"> B12 / (1 + D3) ^ (C12 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -648,11 +648,11 @@
         <v>240</v>
       </c>
       <c r="D13" s="11" t="n">
-        <f aca="false"> B13 / (1 + D3  * C13 / B3)</f>
+        <f aca="false"> B13 / (1 + D3 * C13 / B3)</f>
         <v>0</v>
       </c>
       <c r="E13" s="11" t="n">
-        <f aca="false"> B13 / (1 + D3 ) ^ (C13 / B3)</f>
+        <f aca="false"> B13 / (1 + D3) ^ (C13 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -669,11 +669,11 @@
         <v>270</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false"> B14 / (1 + D3  * C14 / B3)</f>
+        <f aca="false"> B14 / (1 + D3 * C14 / B3)</f>
         <v>0</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false"> B14 / (1 + D3 ) ^ (C14 / B3)</f>
+        <f aca="false"> B14 / (1 + D3) ^ (C14 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -690,11 +690,11 @@
         <v>300</v>
       </c>
       <c r="D15" s="11" t="n">
-        <f aca="false"> B15 / (1 + D3  * C15 / B3)</f>
+        <f aca="false"> B15 / (1 + D3 * C15 / B3)</f>
         <v>0</v>
       </c>
       <c r="E15" s="11" t="n">
-        <f aca="false"> B15 / (1 + D3 ) ^ (C15 / B3)</f>
+        <f aca="false"> B15 / (1 + D3) ^ (C15 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -711,11 +711,11 @@
         <v>330</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false"> B16 / (1 + D3  * C16 / B3)</f>
+        <f aca="false"> B16 / (1 + D3 * C16 / B3)</f>
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false"> B16 / (1 + D3 ) ^ (C16 / B3)</f>
+        <f aca="false"> B16 / (1 + D3) ^ (C16 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -732,11 +732,11 @@
         <v>360</v>
       </c>
       <c r="D17" s="11" t="n">
-        <f aca="false"> B17 / (1 + D3  * C17 / B3)</f>
+        <f aca="false"> B17 / (1 + D3 * C17 / B3)</f>
         <v>0</v>
       </c>
       <c r="E17" s="11" t="n">
-        <f aca="false"> B17 / (1 + D3 ) ^ (C17 / B3)</f>
+        <f aca="false"> B17 / (1 + D3) ^ (C17 / B3)</f>
         <v>0</v>
       </c>
     </row>
@@ -753,11 +753,11 @@
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false"> SUM(D6:D17)</f>
-        <v>2.83170120548341</v>
+        <v>2.73484666677234</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false"> SUM(E6:E17)</f>
-        <v>2.82861135489468</v>
+        <v>2.72727272739002</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -768,11 +768,11 @@
       </c>
       <c r="D19" s="16" t="n">
         <f aca="false">(B18 / D18 - 1)</f>
-        <v>0.0594338110923174</v>
+        <v>0.0969536378215277</v>
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">(B18 / E18 - 1)</f>
-        <v>0.060591089973794</v>
+        <v>0.0999999999526917</v>
       </c>
     </row>
   </sheetData>

--- a/juros.xlsx
+++ b/juros.xlsx
@@ -47,17 +47,17 @@
   </si>
   <si>
     <t xml:space="preserve">Juros Simples
-(amortecimento)</t>
+(amortização)</t>
   </si>
   <si>
     <t xml:space="preserve">Juros Compostos
-(amortecimento)</t>
+(amortização)</t>
   </si>
   <si>
     <t xml:space="preserve">Peso Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso Amortecido</t>
+    <t xml:space="preserve">Pesos Amortizados</t>
   </si>
   <si>
     <t xml:space="preserve">Acréscimos</t>
@@ -458,7 +458,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="n">
-        <v>0.0492122564005581</v>
+        <v>0.03</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -502,11 +502,11 @@
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false"> B6 / (1 + D3 * C6 / B3)</f>
-        <v>0.953095995495338</v>
+        <v>0.970873786407767</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false"> B6 / (1 + D3) ^ (C6 / B3)</f>
-        <v>0.953095995495338</v>
+        <v>0.970873786407767</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -523,11 +523,11 @@
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false"> B7 / (1 + D3 * C7 / B3)</f>
-        <v>0.910394832185489</v>
+        <v>0.943396226415094</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false"> B7 / (1 + D3) ^ (C7 / B3)</f>
-        <v>0.90839197662925</v>
+        <v>0.942595909133754</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -544,11 +544,11 @@
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false"> B8 / (1 + D3 * C8 / B3)</f>
-        <v>0.871355839091515</v>
+        <v>0.91743119266055</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false"> B8 / (1 + D3) ^ (C8 / B3)</f>
-        <v>0.865784755265433</v>
+        <v>0.91514165935316</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -753,11 +753,11 @@
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false"> SUM(D6:D17)</f>
-        <v>2.73484666677234</v>
+        <v>2.83170120548341</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false"> SUM(E6:E17)</f>
-        <v>2.72727272739002</v>
+        <v>2.82861135489468</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -768,11 +768,11 @@
       </c>
       <c r="D19" s="16" t="n">
         <f aca="false">(B18 / D18 - 1)</f>
-        <v>0.0969536378215277</v>
+        <v>0.0594338110923174</v>
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">(B18 / E18 - 1)</f>
-        <v>0.0999999999526917</v>
+        <v>0.060591089973794</v>
       </c>
     </row>
   </sheetData>
